--- a/site/StructureDefinition-hcen-provide-document-bundle.xlsx
+++ b/site/StructureDefinition-hcen-provide-document-bundle.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T01:23:13-03:00</t>
+    <t>2026-10-28T18:02:56-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Bundle de publicación basado en MHD UnContained Comprehensive Provide Document Bundle, adaptado al contrato HCEN con metadatos, documento FHIR y recursos de contexto. La semántica de persistencia de sus entradas debe cerrarse antes de uso operativo.</t>
+    <t>Bundle de publicación basado en MHD UnContained Comprehensive Provide Document Bundle, adaptado al contrato HCEN con metadatos, documento FHIR y recursos de contexto. Plataforma procesa y valida el envío como fachada FHIR y registra metadatos en XDS, sin persistir recursos FHIR.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -263,7 +263,7 @@
   </si>
   <si>
     <t>bdl-1:total only when a search or history {total.empty() or (type = 'searchset') or (type = 'history')}
-bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}hcen-fullurl-unique:Regla local HCEN: cada fullUrl debe ser único, incluso entre recursos con meta.versionId diferentes. {entry.fullUrl.select(toString()).isDistinct()}hcen-publication-current:La publicación inicial contiene referencias documentales en estado current. {entry.resource.ofType(DocumentReference).all(status = 'current')}hcen-publication-fhir-links:Cada DocumentReference se vincula por attachment.url a un único Bundle documental del envío, y cada Bundle documental tiene un único DocumentReference: no hay destinos compartidos ni Bundles huérfanos. {entry.resource.ofType(DocumentReference).all(content.attachment.url.count() = 1) and entry.resource.ofType(DocumentReference).content.attachment.url.select(toString()).isDistinct() and entry.resource.ofType(DocumentReference).content.attachment.url.select(toString()).subsetOf(%context.entry.where(resource is Bundle).fullUrl.select(toString())) and entry.where(resource is Bundle).fullUrl.select(toString()).subsetOf(%context.entry.resource.ofType(DocumentReference).content.attachment.url.select(toString()))}hcen-publication-members:El SubmissionSet enumera todos y solo los DocumentReference del envío por fullUrl exacto, una única vez cada uno y sin imponer orden. {entry.resource.ofType(List).entry.item.all(reference.exists()) and entry.resource.ofType(List).entry.item.reference.select(toString()).isDistinct() and entry.resource.ofType(List).entry.item.reference.select(toString()).subsetOf(%context.entry.where(resource is DocumentReference).fullUrl.select(toString())) and entry.where(resource is DocumentReference).fullUrl.select(toString()).subsetOf(%context.entry.resource.ofType(List).entry.item.reference.select(toString()))}hcen-publication-context:Las referencias explícitas de metadatos HCEN deben resolver a entradas del envío por fullUrl o Tipo/id; no se admiten referencias solo lógicas ni contained como sustituto. {(entry.resource.ofType(DocumentReference).select(subject | author | authenticator | custodian | context.sourcePatientInfo | extension.where(url = 'http://fhir.hcen.gub.uy/StructureDefinition/ext-funder' or url = 'http://fhir.hcen.gub.uy/StructureDefinition/ext-by-order-of').value.ofType(Reference)) | entry.resource.ofType(List).select(subject | source)).all(reference.exists() and reference.select(toString()).subsetOf(%context.entry.fullUrl.select(toString()) | %context.entry.resource.where(id.exists()).select(type().name &amp; '/' &amp; id)))}hcen-publication-contained:Las referencias locales del contexto deben identificar recursos contenidos en el recurso que las aloja. {entry.resource.where(($this is Bundle).not()).all(descendants().ofType(Reference).reference.where(startsWith('#')).select(substring(1)).subsetOf(contained.id.select(toString())))}hcen-publication-authors:La autoría documental incluye un PractitionerRole del envío. Solo los roles usados por author, authenticator o source deben tener Practitioner y Organization como entradas del envío. {entry.resource.ofType(DocumentReference).all(author.reference.select(toString()).intersect(%context.entry.where(resource is PractitionerRole).fullUrl.select(toString()) | %context.entry.resource.ofType(PractitionerRole).where(id.exists()).select('PractitionerRole/' &amp; id)).exists()) and entry.where(resource is PractitionerRole).where((fullUrl.select(toString()) | resource.where(id.exists()).select('PractitionerRole/' &amp; id)).intersect((%context.entry.resource.ofType(DocumentReference).select(author | authenticator) | %context.entry.resource.ofType(List).source).reference.select(toString())).exists()).resource.ofType(PractitionerRole).all(practitioner.reference.exists() and organization.reference.exists() and practitioner.reference.select(toString()).subsetOf(%context.entry.where(resource is Practitioner).fullUrl.select(toString()) | %context.entry.resource.ofType(Practitioner).where(id.exists()).select('Practitioner/' &amp; id)) and organization.reference.select(toString()).subsetOf(%context.entry.where(resource is Organization).fullUrl.select(toString()) | %context.entry.resource.ofType(Organization).where(id.exists()).select('Organization/' &amp; id)))}hcen-publication-document-identifier:El masterIdentifier de cada DocumentReference coincide en system y value con el identifier del Bundle documental vinculado mediante attachment.url. {entry.resource.ofType(DocumentReference).select((content.attachment.url.toString().length().toString() &amp; ':' &amp; content.attachment.url.toString()) &amp; (masterIdentifier.system.toString().length().toString() &amp; ':' &amp; masterIdentifier.system.toString()) &amp; (masterIdentifier.value.toString().length().toString() &amp; ':' &amp; masterIdentifier.value.toString())).subsetOf(%context.entry.where(resource is Bundle).select((fullUrl.toString().length().toString() &amp; ':' &amp; fullUrl.toString()) &amp; (resource.identifier.system.toString().length().toString() &amp; ':' &amp; resource.identifier.system.toString()) &amp; (resource.identifier.value.toString().length().toString() &amp; ':' &amp; resource.identifier.value.toString())))}hcen-publication-submission-entryuuid-member:El entryUUID 2.[oid_documento_clinico] del SubmissionSet corresponde al [oid_documento_clinico] de cualquiera de sus DocumentReference miembros efectivos, sin seleccionar primer miembro ni comparar S. {entry.resource.ofType(List).identifier.where(use = 'official' and system = 'urn:ietf:rfc:3986' and value.startsWith('urn:uuid:')).value.select('urn:oid:' &amp; substring(11)).subsetOf(%context.entry.where(resource is DocumentReference and fullUrl.select(toString()).subsetOf(%context.entry.resource.ofType(List).entry.item.reference.select(toString()))).resource.ofType(DocumentReference).masterIdentifier.value.select(toString()))}</t>
+bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}hcen-fullurl-unique:Regla local HCEN: cada fullUrl debe ser único, incluso entre recursos con meta.versionId diferentes. {entry.fullUrl.select(toString()).isDistinct()}hcen-publication-current:La publicación inicial contiene referencias documentales en estado current. {entry.resource.ofType(DocumentReference).all(status = 'current')}hcen-publication-fhir-links:La correspondencia documental es uno a uno: identificadores completos y distintos en ambos lados y la misma cantidad de DocumentReference y Bundles documentales. Las URL originales FHIR son distintas dentro del envío por comparación exacta. Se complementa con hcen-publication-document-identifier. {entry.resource.ofType(DocumentReference).content.attachment.url.select(toString()).isDistinct() and entry.resource.ofType(DocumentReference).all(masterIdentifier.system.exists() and masterIdentifier.value.exists()) and entry.resource.ofType(Bundle).where(type = 'document').all(identifier.system.exists() and identifier.value.exists()) and entry.resource.ofType(DocumentReference).select((masterIdentifier.system.toString().length().toString() &amp; ':' &amp; masterIdentifier.system.toString()) &amp; (masterIdentifier.value.toString().length().toString() &amp; ':' &amp; masterIdentifier.value.toString())).isDistinct() and entry.resource.ofType(Bundle).where(type = 'document').select((identifier.system.toString().length().toString() &amp; ':' &amp; identifier.system.toString()) &amp; (identifier.value.toString().length().toString() &amp; ':' &amp; identifier.value.toString())).isDistinct() and entry.resource.ofType(DocumentReference).count() = entry.resource.ofType(Bundle).where(type = 'document').count()}hcen-publication-members:El SubmissionSet enumera todos y solo los DocumentReference del envío por fullUrl exacto, una única vez cada uno y sin imponer orden. {entry.resource.ofType(List).entry.item.all(reference.exists()) and entry.resource.ofType(List).entry.item.reference.select(toString()).isDistinct() and entry.resource.ofType(List).entry.item.reference.select(toString()).subsetOf(%context.entry.where(resource is DocumentReference).fullUrl.select(toString())) and entry.where(resource is DocumentReference).fullUrl.select(toString()).subsetOf(%context.entry.resource.ofType(List).entry.item.reference.select(toString()))}hcen-publication-context:Las referencias explícitas de metadatos HCEN deben resolver a entradas del envío por fullUrl o Tipo/id; no se admiten referencias solo lógicas ni contained como sustituto. {(entry.resource.ofType(DocumentReference).select(subject | author | authenticator | custodian | context.sourcePatientInfo | extension.where(url = 'http://fhir.hcen.gub.uy/StructureDefinition/ext-funder' or url = 'http://fhir.hcen.gub.uy/StructureDefinition/ext-by-order-of').value.ofType(Reference)) | entry.resource.ofType(List).select(subject | source)).all(reference.exists() and reference.select(toString()).subsetOf(%context.entry.fullUrl.select(toString()) | %context.entry.resource.where(id.exists()).select(type().name &amp; '/' &amp; id)))}hcen-publication-contained:Las referencias locales del contexto deben identificar recursos contenidos en el recurso que las aloja. {entry.resource.where(($this is Bundle).not()).all(descendants().ofType(Reference).reference.where(startsWith('#')).select(substring(1)).subsetOf(contained.id.select(toString())))}hcen-publication-authors:La autoría documental incluye un PractitionerRole del envío. Solo los roles usados por author, authenticator o source deben tener Practitioner y Organization como entradas del envío. {entry.resource.ofType(DocumentReference).all(author.reference.select(toString()).intersect(%context.entry.where(resource is PractitionerRole).fullUrl.select(toString()) | %context.entry.resource.ofType(PractitionerRole).where(id.exists()).select('PractitionerRole/' &amp; id)).exists()) and entry.where(resource is PractitionerRole).where((fullUrl.select(toString()) | resource.where(id.exists()).select('PractitionerRole/' &amp; id)).intersect((%context.entry.resource.ofType(DocumentReference).select(author | authenticator) | %context.entry.resource.ofType(List).source).reference.select(toString())).exists()).resource.ofType(PractitionerRole).all(practitioner.reference.exists() and organization.reference.exists() and practitioner.reference.select(toString()).subsetOf(%context.entry.where(resource is Practitioner).fullUrl.select(toString()) | %context.entry.resource.ofType(Practitioner).where(id.exists()).select('Practitioner/' &amp; id)) and organization.reference.select(toString()).subsetOf(%context.entry.where(resource is Organization).fullUrl.select(toString()) | %context.entry.resource.ofType(Organization).where(id.exists()).select('Organization/' &amp; id)))}hcen-publication-document-identifier:Los pares system y value de masterIdentifier y Bundle.identifier coinciden en ambos sentidos. Junto con la unicidad y cardinalidad de hcen-publication-fhir-links impide asociaciones ambiguas y documentos huérfanos, independientemente de las URL. {entry.resource.ofType(DocumentReference).select((masterIdentifier.system.toString().length().toString() &amp; ':' &amp; masterIdentifier.system.toString()) &amp; (masterIdentifier.value.toString().length().toString() &amp; ':' &amp; masterIdentifier.value.toString())).subsetOf(%context.entry.resource.ofType(Bundle).where(type = 'document').select((identifier.system.toString().length().toString() &amp; ':' &amp; identifier.system.toString()) &amp; (identifier.value.toString().length().toString() &amp; ':' &amp; identifier.value.toString()))) and entry.resource.ofType(Bundle).where(type = 'document').select((identifier.system.toString().length().toString() &amp; ':' &amp; identifier.system.toString()) &amp; (identifier.value.toString().length().toString() &amp; ':' &amp; identifier.value.toString())).subsetOf(%context.entry.resource.ofType(DocumentReference).select((masterIdentifier.system.toString().length().toString() &amp; ':' &amp; masterIdentifier.system.toString()) &amp; (masterIdentifier.value.toString().length().toString() &amp; ':' &amp; masterIdentifier.value.toString())))}hcen-publication-submission-entryuuid-member:El entryUUID 2.[oid_documento_clinico] del SubmissionSet corresponde al [oid_documento_clinico] de cualquiera de sus DocumentReference miembros efectivos, sin seleccionar primer miembro ni comparar S. {entry.resource.ofType(List).identifier.where(use = 'official' and system = 'urn:ietf:rfc:3986' and value.startsWith('urn:uuid:')).value.select('urn:oid:' &amp; substring(11)).subsetOf(%context.entry.where(resource is DocumentReference and fullUrl.select(toString()).subsetOf(%context.entry.resource.ofType(List).entry.item.reference.select(toString()))).resource.ofType(DocumentReference).masterIdentifier.value.select(toString()))}</t>
   </si>
   <si>
     <t>N/A</t>
@@ -691,10 +691,10 @@
     <t>Bundle.entry.request</t>
   </si>
   <si>
-    <t>Acción propuesta para procesar la entrada</t>
-  </si>
-  <si>
-    <t>Representación preliminar de alta con POST. El contrato de publicación debe resolver la persistencia de las representaciones documentales.</t>
+    <t>Acción transaccional para procesar la entrada</t>
+  </si>
+  <si>
+    <t>Entrada POST del intercambio transaccional. Plataforma registra los metadatos en XDS sin crear un recurso FHIR persistente; los documentos permanecen en el prestador.</t>
   </si>
   <si>
     <t xml:space="preserve">bdl-3
